--- a/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
+++ b/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Addons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$U$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$V$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,12 +100,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="V3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>One-sentence description of the add-on, generated by an AI model from the AnkiWeb description and the GitHub README. Blank = not generated yet.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Anki Addons Dataset</t>
   </si>
@@ -185,6 +198,12 @@
     <t>AI Tools</t>
   </si>
   <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
     <t>NoteSize</t>
   </si>
   <si>
@@ -201,6 +220,9 @@
   </si>
   <si>
     <t>chatgpt</t>
+  </si>
+  <si>
+    <t>Shows the size of the collection and of individual notes.</t>
   </si>
   <si>
     <t>Python, Rust</t>
@@ -585,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -595,7 +617,7 @@
     <col min="6" max="7" width="6.7109375" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
     <col min="12" max="13" width="8.7109375" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" customWidth="1"/>
@@ -605,9 +627,10 @@
     <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="22" max="22" width="80.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +654,7 @@
       </c>
       <c r="N1" s="3"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -659,8 +682,11 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
+      <c r="V2" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:22">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -724,19 +750,22 @@
       <c r="U3" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="V3" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>1188705668</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -751,25 +780,25 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="P4">
         <v>3</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S4">
         <v>5</v>
@@ -778,11 +807,14 @@
         <v>7</v>
       </c>
       <c r="U4" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="V4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:U3"/>
+  <autoFilter ref="A3:V3"/>
   <mergeCells count="8">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>

--- a/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
+++ b/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Addons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$V$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$W$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,12 +113,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="W3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tags chosen by an AI model from a fixed vocabulary, based on the AnkiWeb description and the GitHub README. Blank = not generated yet.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Anki Addons Dataset</t>
   </si>
@@ -204,6 +217,9 @@
     <t>Summary</t>
   </si>
   <si>
+    <t>Tags</t>
+  </si>
+  <si>
     <t>NoteSize</t>
   </si>
   <si>
@@ -223,6 +239,9 @@
   </si>
   <si>
     <t>Shows the size of the collection and of individual notes.</t>
+  </si>
+  <si>
+    <t>statistics</t>
   </si>
   <si>
     <t>Python, Rust</t>
@@ -607,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -628,9 +647,10 @@
     <col min="20" max="20" width="8.7109375" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" customWidth="1"/>
     <col min="22" max="22" width="80.7109375" customWidth="1"/>
+    <col min="23" max="23" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +674,7 @@
       </c>
       <c r="N1" s="3"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -685,8 +705,9 @@
       <c r="V2" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="W2" s="4"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -753,19 +774,22 @@
       <c r="V3" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="W3" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>1188705668</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -780,25 +804,25 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="P4">
         <v>3</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S4">
         <v>5</v>
@@ -807,15 +831,18 @@
         <v>7</v>
       </c>
       <c r="U4" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" t="s">
         <v>36</v>
-      </c>
-      <c r="V4" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V3"/>
-  <mergeCells count="8">
+  <autoFilter ref="A3:W3"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -824,6 +851,7 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:U2"/>
+    <mergeCell ref="V2:W2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1"/>

--- a/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
+++ b/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Addons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$W$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$X$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,7 +61,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="L3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Derived author ID: the smallest ID among the add-ons of the same AnkiWeb author. AnkiWeb does not publish author names. Blank = unknown (snapshots collected before authors were tracked).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -74,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Anki Addons Dataset</t>
   </si>
@@ -176,6 +189,9 @@
   </si>
   <si>
     <t>Declared AI</t>
+  </si>
+  <si>
+    <t>Author</t>
   </si>
   <si>
     <t>Anki Forum</t>
@@ -626,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -638,19 +654,20 @@
     <col min="9" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" customWidth="1"/>
-    <col min="18" max="18" width="50.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" customWidth="1"/>
-    <col min="22" max="22" width="80.7109375" customWidth="1"/>
-    <col min="23" max="23" width="40.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="14" width="8.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
+    <col min="19" max="19" width="50.7109375" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" customWidth="1"/>
+    <col min="22" max="22" width="13.7109375" customWidth="1"/>
+    <col min="23" max="23" width="80.7109375" customWidth="1"/>
+    <col min="24" max="24" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,12 +686,13 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="3">
+      <c r="M1" s="2"/>
+      <c r="N1" s="3">
         <v>46137.60121527778</v>
       </c>
-      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -688,26 +706,27 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="4"/>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -742,16 +761,16 @@
         <v>14</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>20</v>
@@ -772,24 +791,27 @@
         <v>25</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W3" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="X3" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>1188705668</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -804,58 +826,61 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4">
+        <v>1188705668</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4">
+      <c r="Q4">
         <v>3</v>
       </c>
-      <c r="Q4" t="s">
-        <v>30</v>
-      </c>
       <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4">
         <v>5</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>7</v>
       </c>
-      <c r="U4" t="s">
-        <v>38</v>
-      </c>
       <c r="V4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="W4" t="s">
         <v>36</v>
       </c>
+      <c r="X4" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W3"/>
+  <autoFilter ref="A3:X3"/>
   <mergeCells count="9">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:U2"/>
-    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="W2:X2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1"/>
-    <hyperlink ref="O4" r:id="rId2"/>
+    <hyperlink ref="P4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>

--- a/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
+++ b/tests/anki_addons_dataset/exporter/xlsx/exp_data_empty_forum.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Addons" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Addons!$A$3:$Y$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +74,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="M3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>IDs of the add-ons this add-on was forked from, detected from GitHub fork metadata and an AI reading of the AnkiWeb description. Blank = no fork detected, not proof the add-on is original.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="Y3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -144,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Anki Addons Dataset</t>
   </si>
@@ -192,6 +205,9 @@
   </si>
   <si>
     <t>Author</t>
+  </si>
+  <si>
+    <t>Forked from</t>
   </si>
   <si>
     <t>Anki Forum</t>
@@ -642,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -654,20 +670,20 @@
     <col min="9" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="14" width="8.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" customWidth="1"/>
-    <col min="19" max="19" width="50.7109375" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" customWidth="1"/>
-    <col min="23" max="23" width="80.7109375" customWidth="1"/>
-    <col min="24" max="24" width="40.7109375" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="15" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" customWidth="1"/>
+    <col min="17" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" customWidth="1"/>
+    <col min="20" max="20" width="50.7109375" customWidth="1"/>
+    <col min="21" max="21" width="10.7109375" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" customWidth="1"/>
+    <col min="24" max="24" width="80.7109375" customWidth="1"/>
+    <col min="25" max="25" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,12 +703,13 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="3">
+      <c r="N1" s="2"/>
+      <c r="O1" s="3">
         <v>46137.60121527778</v>
       </c>
-      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -707,26 +724,27 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
-      <c r="W2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -764,16 +782,16 @@
         <v>15</v>
       </c>
       <c r="M3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>21</v>
@@ -794,24 +812,27 @@
         <v>26</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="Y3" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:25">
       <c r="A4">
         <v>1188705668</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -826,61 +847,64 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4">
         <v>1188705668</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4">
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4">
         <v>3</v>
       </c>
-      <c r="R4" t="s">
-        <v>31</v>
-      </c>
       <c r="S4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4">
         <v>5</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>7</v>
       </c>
-      <c r="V4" t="s">
-        <v>39</v>
-      </c>
       <c r="W4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="X4" t="s">
         <v>37</v>
       </c>
+      <c r="Y4" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:X3"/>
+  <autoFilter ref="A3:Y3"/>
   <mergeCells count="9">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:V2"/>
-    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="X2:Y2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I4" r:id="rId1"/>
-    <hyperlink ref="P4" r:id="rId2"/>
+    <hyperlink ref="Q4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
